--- a/03_Yetkili_Kullanıcı_Header/3 - AU - HD.xlsx
+++ b/03_Yetkili_Kullanıcı_Header/3 - AU - HD.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bovay\Desktop\¨¨¨¨¨¨\PROJECTS\CV TASLAK\POWER PULSE - PROJE\PLANLAMA\03 - YETKİLİ KULLANICI - HEADER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A63419A-71CF-4EDC-9C38-893409586BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38F90ED-7430-4713-B82C-39474CA5C9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="12090" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="3. GEREKSİNİM TAKİP MATRİKSİ" sheetId="8" r:id="rId1"/>
+    <sheet name="3. GEREKSİNİM TAKİP MATRİSİ" sheetId="8" r:id="rId1"/>
     <sheet name="3.1. YLK BAŞLIK İÇERİĞİ" sheetId="6" r:id="rId2"/>
     <sheet name="3.1.1. AD VE LOGO TIKLANINCA" sheetId="1" r:id="rId3"/>
     <sheet name="3.1.2. KULLANICI BİLGİ BLOK" sheetId="3" r:id="rId4"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="165">
   <si>
     <t>ID</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>Uygulama Adı ve Logosu Tıklandığında Nereye Yönlendiriyor?</t>
-  </si>
-  <si>
-    <t>Düzenleme Simgesi Tıklanınca Edit Profil Düzenleme Penceresi Açılmalı</t>
   </si>
   <si>
     <t>Logout butonu tıklanınca oturum kapatılır, başlangıç sayfası açılır</t>
@@ -232,12 +229,6 @@
     <t>Düzenleme simgesi tıklanır.</t>
   </si>
   <si>
-    <t xml:space="preserve"> Orta</t>
-  </si>
-  <si>
-    <t>Orta</t>
-  </si>
-  <si>
     <t>Logout butonu tıklanabilir olmalı</t>
   </si>
   <si>
@@ -250,9 +241,6 @@
     <t>Kullanıcı başlangıç sayfasını görüntüler</t>
   </si>
   <si>
-    <t>Yüksek (high)</t>
-  </si>
-  <si>
     <t>Yetkili kullanıcı bilgilerine erişilemez</t>
   </si>
   <si>
@@ -400,9 +388,6 @@
     <t>Priority</t>
   </si>
   <si>
-    <t>Test Type</t>
-  </si>
-  <si>
     <t>Checklist ID</t>
   </si>
   <si>
@@ -415,9 +400,6 @@
     <t>Bug ID</t>
   </si>
   <si>
-    <t>3. Gereksinip Takip Matriksi</t>
-  </si>
-  <si>
     <t>RTM - 003 [AU - HD]</t>
   </si>
   <si>
@@ -430,197 +412,6 @@
     <t>Uygulamanın adı ve logosu görüntülenmelidir.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Yetkili kullanıcı için </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Diary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Products</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ve </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Exercises</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> navigasyon öğeleri görüntülenmelidir.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Diary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> navigasyon öğesi görüntülenmelidir.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Products</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> navigasyon öğesi görüntülenmelidir.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Exercises</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> navigasyon öğesi görüntülenmelidir.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Yetkili kullanıcının bulunduğu </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Diary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sayfası aktif olarak vurgulanmalıdır.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Yetkili kullanıcının bulunduğu </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Products</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sayfası aktif olarak vurgulanmalıdır.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Yetkili kullanıcının bulunduğu </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Exercises</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sayfası aktif olarak vurgulanmalıdır.</t>
-    </r>
-  </si>
-  <si>
     <t>Kullanıcının kişisel bilgilerini içeren blok (avatar ve düzenleme simgesi) görüntülenmelidir.</t>
   </si>
   <si>
@@ -654,142 +445,12 @@
     <t>Authentication / Functional</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Backend'de kullanıcı bilgisi bulunduğunda uygulama adına tıklanması kullanıcıyı </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Diary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sayfasına yönlendirmelidir.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Backend'de kullanıcı bilgisi bulunmadığında uygulama adına tıklanması kullanıcıyı </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile Settings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sayfasında bırakmalıdır.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Backend'de kullanıcı bilgisi bulunduğunda uygulama logosuna tıklanması kullanıcıyı </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Diary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sayfasına yönlendirmelidir.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Backend'de kullanıcı bilgisi bulunmadığında uygulama logosuna tıklanması kullanıcıyı </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Profile Settings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sayfasında bırakmalıdır.</t>
-    </r>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
     <t>Test Case</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Düzenleme simgesine tıklanması </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Edit Profile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> düzenleme penceresini açmalıdır.</t>
-    </r>
-  </si>
-  <si>
     <t>Logout butonuna tıklanması kullanıcının oturumunu sonlandırmalıdır.</t>
   </si>
   <si>
@@ -830,9 +491,6 @@
   </si>
   <si>
     <t>BUG - 012 [AU - HD]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sağ kenardan bir burger menü açılır ve menüde navigasyon öğeleri görüntülenirken logout botonu görüntülenmemektedir. </t>
   </si>
   <si>
     <t>Kullanıcı sağ üstte avatarın yanında burger menü simgesini tıklar</t>
@@ -932,17 +590,81 @@
   <si>
     <t>Profil Settings sayfasında kalınır</t>
   </si>
+  <si>
+    <t>Düzenleme Simgesi Tıklanınca (Edit) Profil Düzenleme Penceresi Açılmalı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sağ kenardan bir burger menü açılır ve menüde navigasyon öğeleri görüntülenirken logout butonu görüntülenmemektedir. </t>
+  </si>
+  <si>
+    <t>Document Type</t>
+  </si>
+  <si>
+    <t>3. Gereksinip Takip Matrisi</t>
+  </si>
+  <si>
+    <t>Yetkili kullanıcı için Diary, Products ve Exercises navigasyon öğeleri görüntülenmelidir.</t>
+  </si>
+  <si>
+    <t>Diary navigasyon öğesi görüntülenmelidir.</t>
+  </si>
+  <si>
+    <t>Products navigasyon öğesi görüntülenmelidir.</t>
+  </si>
+  <si>
+    <t>Exercises navigasyon öğesi görüntülenmelidir.</t>
+  </si>
+  <si>
+    <t>Yetkili kullanıcının bulunduğu Diary sayfası aktif olarak vurgulanmalıdır.</t>
+  </si>
+  <si>
+    <t>Yetkili kullanıcının bulunduğu Products sayfası aktif olarak vurgulanmalıdır.</t>
+  </si>
+  <si>
+    <t>Yetkili kullanıcının bulunduğu Exercises sayfası aktif olarak vurgulanmalıdır.</t>
+  </si>
+  <si>
+    <t>Backend'de kullanıcı bilgisi bulunduğunda uygulama adına tıklanması kullanıcıyı Diary sayfasına yönlendirmelidir.</t>
+  </si>
+  <si>
+    <t>Backend'de kullanıcı bilgisi bulunmadığında uygulama adına tıklanması kullanıcıyı Profile Settings sayfasında bırakmalıdır.</t>
+  </si>
+  <si>
+    <t>Backend'de kullanıcı bilgisi bulunduğunda uygulama logosuna tıklanması kullanıcıyı Diary sayfasına yönlendirmelidir.</t>
+  </si>
+  <si>
+    <t>Backend'de kullanıcı bilgisi bulunmadığında uygulama logosuna tıklanması kullanıcıyı Profile Settings sayfasında bırakmalıdır.</t>
+  </si>
+  <si>
+    <t>Düzenleme simgesine tıklanması Edit Profile düzenleme penceresini açmalıdır.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1125,83 +847,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1210,7 +932,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1218,6 +940,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1231,101 +965,85 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1661,7 +1379,7 @@
   <cols>
     <col min="1" max="1" width="19.1796875" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" customWidth="1"/>
     <col min="4" max="4" width="19.1796875" customWidth="1"/>
     <col min="5" max="5" width="16.453125" customWidth="1"/>
     <col min="6" max="6" width="12.90625" customWidth="1"/>
@@ -1671,26 +1389,26 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="80" t="s">
-        <v>105</v>
-      </c>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
+        <v>86</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
       <c r="H1" s="32"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="80" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
+        <v>87</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
       <c r="F2" s="33" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G2" s="32" t="s">
         <v>12</v>
@@ -1699,15 +1417,15 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="80" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
+        <v>89</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
       <c r="F3" s="33" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G3" s="34">
         <v>46225</v>
@@ -1716,18 +1434,18 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="80" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
+        <v>91</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
       <c r="F4" s="31" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H4" s="32"/>
     </row>
@@ -1737,704 +1455,704 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="G7" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" s="36" t="s">
+      <c r="H7" s="20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="85" t="s">
         <v>103</v>
       </c>
-      <c r="G7" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="84" t="s">
-        <v>109</v>
-      </c>
       <c r="B8" s="38" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E8" s="83" t="s">
-        <v>122</v>
+        <v>127</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>109</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G8" s="83" t="s">
-        <v>122</v>
+        <v>110</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>109</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="79" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="85" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="B9" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E9" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G9" s="83" t="s">
-        <v>122</v>
+      <c r="G9" s="39" t="s">
+        <v>109</v>
       </c>
       <c r="H9" s="38" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="85" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E10" s="83" t="s">
-        <v>122</v>
+        <v>127</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>109</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G10" s="83" t="s">
-        <v>122</v>
+        <v>110</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>109</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="85" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E11" s="83" t="s">
-        <v>122</v>
+        <v>127</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>109</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G11" s="83" t="s">
-        <v>122</v>
+        <v>110</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>109</v>
       </c>
       <c r="H11" s="38" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="85" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="B12" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="38" t="s">
+    </row>
+    <row r="13" spans="1:8" ht="73" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="85" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="71" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="85" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="85" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" s="38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="80.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="85" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="85" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="66.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="85" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="85" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="38" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="120.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="85" t="s">
+        <v>160</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H20" s="38" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="132.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="85" t="s">
+        <v>161</v>
+      </c>
+      <c r="B21" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="38" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="85" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H22" s="38" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="85" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H23" s="38" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="95.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="85" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H24" s="38" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="111" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="85" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H25" s="38" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="85" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H26" s="38" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="85" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="38" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="85" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28" s="38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="86" t="s">
         <v>121</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E12" s="83" t="s">
+      <c r="B29" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H29" s="38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="88" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="85" t="s">
         <v>122</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="B30" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G30" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="38" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="108" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="85" t="s">
         <v>123</v>
       </c>
-      <c r="G12" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="73" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="84" t="s">
+      <c r="B31" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E31" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G13" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H13" s="38" t="s">
+    </row>
+    <row r="32" spans="1:8" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="85" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" s="38" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="85" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="71" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="84" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D14" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E14" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G14" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="84" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D15" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E15" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F15" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G15" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H15" s="38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="80.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="84" t="s">
-        <v>117</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E16" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G16" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="84" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G17" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="66.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="84" t="s">
-        <v>119</v>
-      </c>
-      <c r="B18" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G18" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="84" t="s">
-        <v>120</v>
-      </c>
-      <c r="B19" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E19" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F19" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G19" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H19" s="38" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="120.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="84" t="s">
+      <c r="B33" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="F33" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G20" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="132.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="84" t="s">
+      <c r="G33" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="B21" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G21" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H21" s="38" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="84" t="s">
-        <v>130</v>
-      </c>
-      <c r="B22" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="D22" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="E22" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G22" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="84" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="D23" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G23" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H23" s="38" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="95.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="82" t="s">
-        <v>134</v>
-      </c>
-      <c r="B24" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="D24" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G24" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="111" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="84" t="s">
-        <v>135</v>
-      </c>
-      <c r="B25" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="D25" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="E25" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G25" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H25" s="38" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="84" t="s">
-        <v>136</v>
-      </c>
-      <c r="B26" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="D26" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="E26" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G26" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H26" s="38" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="84" t="s">
-        <v>137</v>
-      </c>
-      <c r="B27" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="D27" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G27" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H27" s="38" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="82" t="s">
-        <v>138</v>
-      </c>
-      <c r="B28" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F28" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G28" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H28" s="38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="81" t="s">
-        <v>139</v>
-      </c>
-      <c r="B29" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="E29" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F29" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G29" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H29" s="38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="88" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="82" t="s">
-        <v>140</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="E30" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F30" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G30" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H30" s="38" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="108" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="82" t="s">
-        <v>141</v>
-      </c>
-      <c r="B31" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="E31" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F31" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G31" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H31" s="38" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="82" t="s">
-        <v>142</v>
-      </c>
-      <c r="B32" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="E32" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F32" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="G32" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="H32" s="38" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="82" t="s">
-        <v>143</v>
-      </c>
-      <c r="B33" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="E33" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="F33" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="G33" s="32" t="s">
-        <v>147</v>
-      </c>
       <c r="H33" s="38" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="100" customHeight="1" x14ac:dyDescent="0.35">
@@ -2639,16 +2357,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
+      <c r="A1" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
       <c r="D1" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -2659,13 +2377,13 @@
       <c r="E2" s="10"/>
     </row>
     <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" s="46"/>
+      <c r="A3" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="50"/>
       <c r="C3" s="16"/>
       <c r="D3" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>12</v>
@@ -2679,44 +2397,44 @@
       <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48" t="s">
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="47" t="s">
+      <c r="B6" s="51"/>
+      <c r="C6" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="47" t="s">
+      <c r="B7" s="51"/>
+      <c r="C7" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
     </row>
     <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="49"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
     </row>
     <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="17"/>
@@ -2726,142 +2444,142 @@
       <c r="E9" s="17"/>
     </row>
     <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
+      <c r="A10" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
       <c r="D10" s="18"/>
       <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="41"/>
+      <c r="A11" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="45"/>
       <c r="C11" s="22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
     </row>
     <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="41" t="s">
-        <v>161</v>
-      </c>
-      <c r="B12" s="41"/>
+      <c r="A12" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="B12" s="45"/>
       <c r="C12" s="22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
     </row>
     <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="42" t="s">
-        <v>162</v>
-      </c>
-      <c r="B13" s="43"/>
+      <c r="A13" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="47"/>
       <c r="C13" s="22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
     </row>
     <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="43"/>
+      <c r="A14" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="47"/>
       <c r="C14" s="22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
     </row>
     <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="43"/>
+      <c r="A15" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="47"/>
       <c r="C15" s="22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
     </row>
     <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="B16" s="40"/>
+      <c r="A16" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" s="44"/>
       <c r="C16" s="22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
     </row>
     <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="40"/>
+      <c r="A17" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="44"/>
       <c r="C17" s="22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="40"/>
+      <c r="A18" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="44"/>
       <c r="C18" s="22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="41"/>
+      <c r="A19" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="45"/>
       <c r="C19" s="22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
     </row>
     <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="43"/>
+      <c r="A20" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="47"/>
       <c r="C20" s="22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
     </row>
     <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="43"/>
+      <c r="A21" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="47"/>
       <c r="C21" s="22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="41"/>
+      <c r="A22" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="45"/>
       <c r="C22" s="22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
@@ -2914,99 +2632,99 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="54"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="58"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="54"/>
+      <c r="B3" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="58"/>
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="52" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54"/>
+      <c r="E3" s="56" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58"/>
     </row>
     <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="54"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="58"/>
     </row>
     <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="54"/>
+      <c r="B5" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="58"/>
     </row>
     <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="54"/>
+      <c r="B6" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="58"/>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="59"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="63"/>
     </row>
     <row r="8" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="60" t="s">
+      <c r="C8" s="60"/>
+      <c r="D8" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="61"/>
+      <c r="E8" s="65"/>
       <c r="F8" s="1" t="s">
         <v>8</v>
       </c>
@@ -3021,16 +2739,16 @@
       <c r="A9" s="1">
         <v>1</v>
       </c>
-      <c r="B9" s="52" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="E9" s="54"/>
+      <c r="B9" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="58"/>
+      <c r="D9" s="56" t="s">
+        <v>145</v>
+      </c>
+      <c r="E9" s="58"/>
       <c r="F9" s="23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -3039,16 +2757,16 @@
       <c r="A10" s="1">
         <v>2</v>
       </c>
-      <c r="B10" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="E10" s="54"/>
+      <c r="B10" s="56" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="58"/>
+      <c r="D10" s="56" t="s">
+        <v>148</v>
+      </c>
+      <c r="E10" s="58"/>
       <c r="F10" s="23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -3057,16 +2775,16 @@
       <c r="A11" s="1">
         <v>3</v>
       </c>
-      <c r="B11" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="E11" s="54"/>
+      <c r="B11" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="58"/>
+      <c r="D11" s="56" t="s">
+        <v>145</v>
+      </c>
+      <c r="E11" s="58"/>
       <c r="F11" s="23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -3075,16 +2793,16 @@
       <c r="A12" s="1">
         <v>4</v>
       </c>
-      <c r="B12" s="52" t="s">
-        <v>158</v>
-      </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="E12" s="54"/>
+      <c r="B12" s="56" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="58"/>
+      <c r="D12" s="56" t="s">
+        <v>148</v>
+      </c>
+      <c r="E12" s="58"/>
       <c r="F12" s="23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -3093,10 +2811,10 @@
       <c r="A13" s="1">
         <v>5</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="54"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="58"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -3105,10 +2823,10 @@
       <c r="A14" s="1">
         <v>6</v>
       </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="54"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="58"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -3117,10 +2835,10 @@
       <c r="A15" s="1">
         <v>7</v>
       </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="54"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="58"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -3130,16 +2848,16 @@
         <v>11</v>
       </c>
       <c r="B16" s="1"/>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="54"/>
+      <c r="D16" s="58"/>
       <c r="E16" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F16" s="53"/>
-      <c r="G16" s="53"/>
-      <c r="H16" s="54"/>
+        <v>140</v>
+      </c>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -3189,99 +2907,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="54"/>
+      <c r="D1" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="58"/>
     </row>
     <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="52" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="54"/>
+      <c r="B2" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="58"/>
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="54"/>
+      <c r="E2" s="56" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="58"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58"/>
     </row>
     <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="54"/>
+      <c r="B4" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="58"/>
     </row>
     <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="54"/>
+      <c r="B5" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="58"/>
     </row>
     <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="59"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="63"/>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="56"/>
-      <c r="D7" s="57" t="s">
+      <c r="C7" s="60"/>
+      <c r="D7" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="56"/>
+      <c r="E7" s="60"/>
       <c r="F7" s="3" t="s">
         <v>8</v>
       </c>
@@ -3296,16 +3014,16 @@
       <c r="A8" s="1">
         <v>1</v>
       </c>
-      <c r="B8" s="52" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="54"/>
-      <c r="D8" s="52" t="s">
+      <c r="B8" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="54"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="58"/>
       <c r="F8" s="23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -3314,10 +3032,10 @@
       <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="B9" s="52"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="54"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="58"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -3326,10 +3044,10 @@
       <c r="A10" s="1">
         <v>3</v>
       </c>
-      <c r="B10" s="52"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="54"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="58"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -3338,10 +3056,10 @@
       <c r="A11" s="1">
         <v>4</v>
       </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="54"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="58"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -3350,10 +3068,10 @@
       <c r="A12" s="1">
         <v>5</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="54"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="58"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -3362,10 +3080,10 @@
       <c r="A13" s="1">
         <v>6</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="54"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="58"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -3374,10 +3092,10 @@
       <c r="A14" s="1">
         <v>7</v>
       </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="54"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="58"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -3387,18 +3105,18 @@
         <v>11</v>
       </c>
       <c r="B15" s="1"/>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="54"/>
+      <c r="D15" s="58"/>
       <c r="E15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="87">
+      <c r="F15" s="66">
         <v>46225</v>
       </c>
-      <c r="G15" s="88"/>
-      <c r="H15" s="63"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -3450,95 +3168,95 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="54"/>
+      <c r="D1" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="58"/>
     </row>
     <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="54"/>
+      <c r="B2" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="58"/>
       <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="52" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="54"/>
+      <c r="E2" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="58"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="61"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="54"/>
+      <c r="B4" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="58"/>
     </row>
     <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="52" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="54"/>
+      <c r="B5" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="58"/>
     </row>
     <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="59"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="63"/>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
-      <c r="B7" s="60" t="s">
+      <c r="B7" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="61"/>
+      <c r="C7" s="65"/>
       <c r="D7" s="3" t="s">
         <v>7</v>
       </c>
@@ -3557,16 +3275,16 @@
       <c r="A8" s="1">
         <v>1</v>
       </c>
-      <c r="B8" s="52" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="54"/>
-      <c r="D8" s="52" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="54"/>
+      <c r="B8" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="58"/>
+      <c r="D8" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="58"/>
       <c r="F8" s="23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -3575,16 +3293,16 @@
       <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="B9" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="52" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="54"/>
+      <c r="B9" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="58"/>
+      <c r="D9" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="58"/>
       <c r="F9" s="23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -3593,10 +3311,10 @@
       <c r="A10" s="1">
         <v>3</v>
       </c>
-      <c r="B10" s="52"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="54"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="58"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -3605,10 +3323,10 @@
       <c r="A11" s="1">
         <v>4</v>
       </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="54"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="58"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -3617,10 +3335,10 @@
       <c r="A12" s="1">
         <v>5</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="54"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="58"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -3629,10 +3347,10 @@
       <c r="A13" s="1">
         <v>6</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="54"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="58"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -3641,31 +3359,31 @@
       <c r="A14" s="1">
         <v>7</v>
       </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="54"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="58"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="65" t="s">
+      <c r="A15" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="52" t="s">
+      <c r="B15" s="72"/>
+      <c r="C15" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="54"/>
+      <c r="D15" s="58"/>
       <c r="E15" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="86">
+      <c r="F15" s="66">
         <v>46225</v>
       </c>
-      <c r="G15" s="53"/>
-      <c r="H15" s="54"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -3712,16 +3430,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
+      <c r="A1" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
       <c r="D1" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -3732,13 +3450,13 @@
       <c r="E2" s="8"/>
     </row>
     <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="46"/>
+      <c r="A3" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="50"/>
       <c r="C3" s="11"/>
       <c r="D3" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>12</v>
@@ -3752,44 +3470,44 @@
       <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48" t="s">
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="47" t="s">
+      <c r="B6" s="51"/>
+      <c r="C6" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="47" t="s">
+      <c r="B7" s="51"/>
+      <c r="C7" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
     </row>
     <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="49"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
     </row>
     <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
@@ -3799,89 +3517,89 @@
       <c r="E9" s="14"/>
     </row>
     <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="68" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="69"/>
+      <c r="A10" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="75"/>
       <c r="C10" s="20" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="67" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="67"/>
+      <c r="A11" s="73" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="73"/>
       <c r="C11" s="24" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D11" s="26"/>
       <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="41"/>
+      <c r="A12" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="45"/>
       <c r="C12" s="24" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="14"/>
     </row>
     <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="67" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="67"/>
+      <c r="A13" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="73"/>
       <c r="C13" s="24" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="14"/>
     </row>
     <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="67" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="67"/>
+      <c r="A14" s="73" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="73"/>
       <c r="C14" s="24" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="67" t="s">
+      <c r="A15" s="73" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="73"/>
+      <c r="C15" s="24" t="s">
         <v>54</v>
-      </c>
-      <c r="B15" s="67"/>
-      <c r="C15" s="24" t="s">
-        <v>58</v>
       </c>
       <c r="D15" s="26"/>
       <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="67" t="s">
+      <c r="A16" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="73"/>
+      <c r="C16" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="67"/>
-      <c r="C16" s="24" t="s">
-        <v>59</v>
-      </c>
       <c r="D16" s="27" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="E16" s="14"/>
     </row>
     <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="51"/>
-      <c r="B17" s="51"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="55"/>
       <c r="C17" s="19"/>
       <c r="D17" s="26"/>
       <c r="E17" s="14"/>
@@ -3927,346 +3645,346 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
+        <v>130</v>
+      </c>
+      <c r="C1" s="77"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="28" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B2" s="29" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D2" s="29"/>
       <c r="E2" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="F2" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+        <v>61</v>
+      </c>
+      <c r="F2" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="80"/>
+      <c r="H2" s="81"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="28" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="F3" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="74"/>
-      <c r="H3" s="75"/>
+        <v>65</v>
+      </c>
+      <c r="F3" s="79" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="80"/>
+      <c r="H3" s="81"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="75"/>
+        <v>66</v>
+      </c>
+      <c r="B4" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="81"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="70" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
+        <v>67</v>
+      </c>
+      <c r="B5" s="76" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
+        <v>68</v>
+      </c>
+      <c r="B6" s="76" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="73" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="76"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="77"/>
+      <c r="A7" s="79" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="83"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="78"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="78"/>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="78"/>
+      <c r="B8" s="84"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="28">
         <v>1</v>
       </c>
-      <c r="B9" s="70" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
+      <c r="B9" s="76" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="28">
         <v>2</v>
       </c>
-      <c r="B10" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
+      <c r="B10" s="76" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="78" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
+      <c r="A11" s="84" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="84"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="28">
         <v>1</v>
       </c>
-      <c r="B12" s="70" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
+      <c r="B12" s="76" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="28">
         <v>2</v>
       </c>
-      <c r="B13" s="70" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
+      <c r="B13" s="76" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="28">
         <v>3</v>
       </c>
-      <c r="B14" s="70" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="70"/>
+      <c r="B14" s="76" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="76"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="28">
         <v>4</v>
       </c>
-      <c r="B15" s="70"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="28">
         <v>5</v>
       </c>
-      <c r="B16" s="70"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70"/>
-      <c r="H16" s="70"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="76"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="76"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="78" t="s">
-        <v>151</v>
-      </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
+      <c r="A17" s="84" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="84"/>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="84"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="70" t="s">
-        <v>152</v>
-      </c>
-      <c r="B18" s="70"/>
-      <c r="C18" s="70"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
+      <c r="A18" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="76"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="70"/>
-      <c r="B19" s="70"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="70"/>
+      <c r="A19" s="76"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="76"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="70"/>
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
+      <c r="A20" s="76"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="76"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="78" t="s">
-        <v>153</v>
-      </c>
-      <c r="B21" s="78"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="78"/>
-      <c r="H21" s="78"/>
+      <c r="A21" s="84" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="84"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="84"/>
+      <c r="E21" s="84"/>
+      <c r="F21" s="84"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="84"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="70" t="s">
-        <v>154</v>
-      </c>
-      <c r="B22" s="70"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="70"/>
+      <c r="A22" s="76" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" s="76"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="70"/>
-      <c r="B23" s="70"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="A23" s="76"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="70"/>
-      <c r="B24" s="70"/>
-      <c r="C24" s="70"/>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="70"/>
-      <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
+      <c r="A24" s="76"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
     </row>
     <row r="25" spans="1:8" ht="360.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="70"/>
-      <c r="C25" s="70"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
+        <v>70</v>
+      </c>
+      <c r="B25" s="76"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="70" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
+        <v>71</v>
+      </c>
+      <c r="B26" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="76"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="76"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="30"/>

--- a/03_Yetkili_Kullanıcı_Header/3 - AU - HD.xlsx
+++ b/03_Yetkili_Kullanıcı_Header/3 - AU - HD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bovay\Desktop\¨¨¨¨¨¨\PROJECTS\CV TASLAK\POWER PULSE - PROJE\PLANLAMA\03 - YETKİLİ KULLANICI - HEADER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38F90ED-7430-4713-B82C-39474CA5C9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B4DFC5-E38E-42BB-B63A-5EF67B9528EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3. GEREKSİNİM TAKİP MATRİSİ" sheetId="8" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="166">
   <si>
     <t>ID</t>
   </si>
@@ -478,9 +478,6 @@
     <t>Tablet görünümde burger menü içerisinde Logout butonu görüntülenmelidir.</t>
   </si>
   <si>
-    <t xml:space="preserve">CL - 006 [AU - HD] </t>
-  </si>
-  <si>
     <t>CL - 006 [AU - HD]</t>
   </si>
   <si>
@@ -542,9 +539,6 @@
   </si>
   <si>
     <t>Uygulama logosuna tıklanır (backend'de kullanıcı bilgisi yok)</t>
-  </si>
-  <si>
-    <t>Date: 22.07.2026</t>
   </si>
   <si>
     <r>
@@ -637,6 +631,15 @@
   </si>
   <si>
     <t>Düzenleme simgesine tıklanması Edit Profile düzenleme penceresini açmalıdır.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 22.07.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL - 007 [AU - HD] </t>
+  </si>
+  <si>
+    <t>CL - 008 [AU - HD]</t>
   </si>
 </sst>
 </file>
@@ -847,7 +850,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -857,7 +860,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -944,6 +946,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1002,6 +1010,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1015,12 +1027,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1039,12 +1045,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1388,951 +1388,951 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="H1" s="31"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="F2" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="F3" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="33">
+        <v>46225</v>
+      </c>
+      <c r="H3" s="31"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="F4" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="31"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="30"/>
+      <c r="H5" s="31"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F8" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H8" s="37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="79" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="H1" s="32"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="F2" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="32"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="F3" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="34">
-        <v>46225</v>
-      </c>
-      <c r="H3" s="32"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="F4" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="G4" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="H4" s="32"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="31"/>
-      <c r="H5" s="32"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="F7" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="38" t="s">
+      <c r="B10" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C10" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D10" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="73" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="71" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E15" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="80.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="66.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="120.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="132.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="95.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="111" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="37" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="88" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G30" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="108" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E31" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" s="37" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F33" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="79" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="85" t="s">
-        <v>153</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H9" s="38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="85" t="s">
-        <v>154</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D10" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="85" t="s">
-        <v>155</v>
-      </c>
-      <c r="B11" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H11" s="38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="85" t="s">
-        <v>156</v>
-      </c>
-      <c r="B12" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="73" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="85" t="s">
-        <v>157</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H13" s="38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="71" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="85" t="s">
-        <v>158</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="85" t="s">
-        <v>159</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F15" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H15" s="38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="80.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="85" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="85" t="s">
-        <v>105</v>
-      </c>
-      <c r="B17" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F17" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="66.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="85" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H18" s="38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="85" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D19" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F19" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H19" s="38" t="s">
+      <c r="G33" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="H33" s="37" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="120.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="85" t="s">
-        <v>160</v>
-      </c>
-      <c r="B20" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G20" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="132.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="85" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="E21" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H21" s="38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="85" t="s">
-        <v>162</v>
-      </c>
-      <c r="B22" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G22" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="125.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="85" t="s">
-        <v>163</v>
-      </c>
-      <c r="B23" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G23" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H23" s="38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="95.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="85" t="s">
-        <v>164</v>
-      </c>
-      <c r="B24" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G24" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="111" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="85" t="s">
-        <v>117</v>
-      </c>
-      <c r="B25" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="E25" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="F25" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G25" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H25" s="38" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="85" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="E26" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G26" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H26" s="38" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="85" t="s">
-        <v>119</v>
-      </c>
-      <c r="B27" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="F27" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G27" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H27" s="38" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="98.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="85" t="s">
-        <v>120</v>
-      </c>
-      <c r="B28" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F28" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G28" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H28" s="38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="86" t="s">
-        <v>121</v>
-      </c>
-      <c r="B29" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F29" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G29" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H29" s="38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="88" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="85" t="s">
-        <v>122</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="E30" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F30" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G30" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H30" s="38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="108" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="85" t="s">
-        <v>123</v>
-      </c>
-      <c r="B31" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="E31" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F31" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H31" s="38" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="85" t="s">
-        <v>124</v>
-      </c>
-      <c r="B32" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="E32" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F32" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G32" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="H32" s="38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="85" t="s">
-        <v>125</v>
-      </c>
-      <c r="B33" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F33" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="G33" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="H33" s="38" t="s">
-        <v>114</v>
-      </c>
-    </row>
     <row r="34" spans="1:8" ht="100" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="37"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
+      <c r="A34" s="36"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
     </row>
     <row r="35" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
+      <c r="A35" s="36"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
     </row>
     <row r="36" spans="1:8" ht="101.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="37"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
+      <c r="A36" s="36"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
     </row>
     <row r="37" spans="1:8" ht="108" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
+      <c r="B37" s="37"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
     </row>
     <row r="38" spans="1:8" ht="111" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="37"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
+      <c r="A38" s="36"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="37"/>
     </row>
     <row r="39" spans="1:8" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="37"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
+      <c r="A39" s="36"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="37"/>
     </row>
     <row r="40" spans="1:8" ht="113.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="37"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
+      <c r="A40" s="36"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="37"/>
     </row>
     <row r="41" spans="1:8" ht="106.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="37"/>
-      <c r="B41" s="38"/>
-      <c r="C41" s="38"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
+      <c r="A41" s="36"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
     </row>
     <row r="42" spans="1:8" ht="97" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="37"/>
-      <c r="B42" s="38"/>
-      <c r="C42" s="38"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
+      <c r="A42" s="36"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
     </row>
     <row r="43" spans="1:8" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="37"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
+      <c r="A43" s="36"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
     </row>
     <row r="44" spans="1:8" ht="78.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="37"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="38"/>
+      <c r="A44" s="36"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
     </row>
     <row r="45" spans="1:8" ht="95.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="37"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="38"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="38"/>
+      <c r="A45" s="36"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
     </row>
     <row r="46" spans="1:8" ht="115.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="37"/>
-      <c r="B46" s="38"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
+      <c r="A46" s="36"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="37"/>
     </row>
     <row r="47" spans="1:8" ht="100" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="37"/>
-      <c r="B47" s="38"/>
-      <c r="C47" s="38"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
+      <c r="A47" s="36"/>
+      <c r="B47" s="37"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="37"/>
     </row>
     <row r="48" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="37"/>
-      <c r="B48" s="38"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
+      <c r="A48" s="36"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="37"/>
     </row>
     <row r="49" spans="1:8" ht="109" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="37"/>
-      <c r="B49" s="38"/>
-      <c r="C49" s="38"/>
-      <c r="D49" s="38"/>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="38"/>
+      <c r="A49" s="36"/>
+      <c r="B49" s="37"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="37"/>
+      <c r="H49" s="37"/>
     </row>
     <row r="50" spans="1:8" ht="104.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="37"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
+      <c r="A50" s="36"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="37"/>
     </row>
     <row r="51" spans="1:8" ht="112" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="37"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="38"/>
-      <c r="D51" s="38"/>
-      <c r="E51" s="38"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="38"/>
+      <c r="A51" s="36"/>
+      <c r="B51" s="37"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2357,232 +2357,232 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="15" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>126</v>
+      <c r="E1" s="9" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="9"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
     </row>
     <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="51"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="52"/>
+      <c r="C5" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="52"/>
+      <c r="C7" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+    </row>
+    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="54"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+    </row>
+    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="46"/>
+      <c r="C11" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="46"/>
+      <c r="C12" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-    </row>
-    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="51" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="52" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="52" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-    </row>
-    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="53"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-    </row>
-    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="17"/>
-    </row>
-    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="45"/>
-      <c r="C11" s="22" t="s">
+      <c r="B13" s="48"/>
+      <c r="C13" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="45" t="s">
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="48"/>
+      <c r="C14" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+    </row>
+    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="48"/>
+      <c r="C15" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="22" t="s">
+      <c r="B16" s="45"/>
+      <c r="C16" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-    </row>
-    <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="22" t="s">
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="45"/>
+      <c r="C17" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-    </row>
-    <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="22" t="s">
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="45"/>
+      <c r="C18" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="22" t="s">
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="46"/>
+      <c r="C19" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-    </row>
-    <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="43" t="s">
-        <v>144</v>
-      </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="22" t="s">
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="48"/>
+      <c r="C20" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="22" t="s">
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="48"/>
+      <c r="C21" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="44"/>
-      <c r="C18" s="22" t="s">
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="46"/>
+      <c r="C22" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="45"/>
-      <c r="C19" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="47"/>
-      <c r="C20" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -2637,94 +2637,94 @@
       <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="58"/>
+      <c r="C3" s="59"/>
       <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="59"/>
     </row>
     <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="58"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="59"/>
     </row>
     <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="59"/>
     </row>
     <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="59"/>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="63"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="64"/>
     </row>
     <row r="8" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="64" t="s">
+      <c r="C8" s="61"/>
+      <c r="D8" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="65"/>
+      <c r="E8" s="66"/>
       <c r="F8" s="1" t="s">
         <v>8</v>
       </c>
@@ -2739,15 +2739,15 @@
       <c r="A9" s="1">
         <v>1</v>
       </c>
-      <c r="B9" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="23" t="s">
+      <c r="B9" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="59"/>
+      <c r="D9" s="57" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" s="59"/>
+      <c r="F9" s="22" t="s">
         <v>54</v>
       </c>
       <c r="G9" s="1"/>
@@ -2757,15 +2757,15 @@
       <c r="A10" s="1">
         <v>2</v>
       </c>
-      <c r="B10" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="E10" s="58"/>
-      <c r="F10" s="23" t="s">
+      <c r="B10" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="59"/>
+      <c r="D10" s="57" t="s">
+        <v>146</v>
+      </c>
+      <c r="E10" s="59"/>
+      <c r="F10" s="22" t="s">
         <v>54</v>
       </c>
       <c r="G10" s="1"/>
@@ -2775,15 +2775,15 @@
       <c r="A11" s="1">
         <v>3</v>
       </c>
-      <c r="B11" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="E11" s="58"/>
-      <c r="F11" s="23" t="s">
+      <c r="B11" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="59"/>
+      <c r="D11" s="57" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" s="59"/>
+      <c r="F11" s="22" t="s">
         <v>54</v>
       </c>
       <c r="G11" s="1"/>
@@ -2793,15 +2793,15 @@
       <c r="A12" s="1">
         <v>4</v>
       </c>
-      <c r="B12" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="E12" s="58"/>
-      <c r="F12" s="23" t="s">
+      <c r="B12" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" s="59"/>
+      <c r="D12" s="57" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" s="59"/>
+      <c r="F12" s="22" t="s">
         <v>54</v>
       </c>
       <c r="G12" s="1"/>
@@ -2811,10 +2811,10 @@
       <c r="A13" s="1">
         <v>5</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="58"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="59"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -2823,10 +2823,10 @@
       <c r="A14" s="1">
         <v>6</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="58"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="59"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -2835,10 +2835,10 @@
       <c r="A15" s="1">
         <v>7</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="58"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="59"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -2847,45 +2847,48 @@
       <c r="A16" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="56" t="s">
+      <c r="B16" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="58"/>
-      <c r="E16" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="58"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="68"/>
+      <c r="F16" s="67" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" s="67"/>
+      <c r="H16" s="67"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D9:E9"/>
+  <mergeCells count="26">
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D16:E16"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B6:H6"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2896,6 +2899,7 @@
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="9.7265625" customWidth="1"/>
     <col min="2" max="2" width="21.453125" customWidth="1"/>
     <col min="3" max="3" width="19.54296875" customWidth="1"/>
     <col min="5" max="5" width="30.6328125" customWidth="1"/>
@@ -2912,94 +2916,94 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="58"/>
+      <c r="D1" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="58"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="58"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="59"/>
     </row>
     <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="59"/>
     </row>
     <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="59"/>
     </row>
     <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="63"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="64"/>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="61" t="s">
+      <c r="C7" s="61"/>
+      <c r="D7" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="60"/>
+      <c r="E7" s="61"/>
       <c r="F7" s="3" t="s">
         <v>8</v>
       </c>
@@ -3014,15 +3018,15 @@
       <c r="A8" s="1">
         <v>1</v>
       </c>
-      <c r="B8" s="56" t="s">
+      <c r="B8" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="56" t="s">
+      <c r="C8" s="59"/>
+      <c r="D8" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="23" t="s">
+      <c r="E8" s="59"/>
+      <c r="F8" s="22" t="s">
         <v>54</v>
       </c>
       <c r="G8" s="1"/>
@@ -3032,10 +3036,10 @@
       <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="B9" s="56"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="58"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="59"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -3044,10 +3048,10 @@
       <c r="A10" s="1">
         <v>3</v>
       </c>
-      <c r="B10" s="56"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="58"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="59"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -3056,10 +3060,10 @@
       <c r="A11" s="1">
         <v>4</v>
       </c>
-      <c r="B11" s="69"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="58"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="59"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -3068,10 +3072,10 @@
       <c r="A12" s="1">
         <v>5</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="58"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="59"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -3080,10 +3084,10 @@
       <c r="A13" s="1">
         <v>6</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="58"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="59"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -3092,10 +3096,10 @@
       <c r="A14" s="1">
         <v>7</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="58"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="59"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -3104,22 +3108,22 @@
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="56" t="s">
+      <c r="B15" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="58"/>
-      <c r="E15" s="2" t="s">
+      <c r="C15" s="67"/>
+      <c r="D15" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="66">
+      <c r="E15" s="68"/>
+      <c r="F15" s="69">
         <v>46225</v>
       </c>
-      <c r="G15" s="67"/>
-      <c r="H15" s="68"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="71"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:E10"/>
@@ -3131,7 +3135,8 @@
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="D14:E14"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -3156,6 +3161,7 @@
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="10.6328125" customWidth="1"/>
     <col min="2" max="2" width="21.54296875" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="10.81640625" customWidth="1"/>
@@ -3173,90 +3179,90 @@
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="59"/>
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="56" t="s">
+      <c r="E2" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="65"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="66"/>
     </row>
     <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="59"/>
     </row>
     <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="59"/>
     </row>
     <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="63"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="64"/>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="65"/>
+      <c r="C7" s="66"/>
       <c r="D7" s="3" t="s">
         <v>7</v>
       </c>
@@ -3275,15 +3281,15 @@
       <c r="A8" s="1">
         <v>1</v>
       </c>
-      <c r="B8" s="56" t="s">
+      <c r="B8" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="56" t="s">
+      <c r="C8" s="59"/>
+      <c r="D8" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="23" t="s">
+      <c r="E8" s="59"/>
+      <c r="F8" s="22" t="s">
         <v>54</v>
       </c>
       <c r="G8" s="1"/>
@@ -3293,15 +3299,15 @@
       <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="56" t="s">
+      <c r="C9" s="59"/>
+      <c r="D9" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="23" t="s">
+      <c r="E9" s="59"/>
+      <c r="F9" s="22" t="s">
         <v>54</v>
       </c>
       <c r="G9" s="1"/>
@@ -3311,10 +3317,10 @@
       <c r="A10" s="1">
         <v>3</v>
       </c>
-      <c r="B10" s="56"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="58"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="59"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -3323,10 +3329,10 @@
       <c r="A11" s="1">
         <v>4</v>
       </c>
-      <c r="B11" s="69"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="58"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="59"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -3335,10 +3341,10 @@
       <c r="A12" s="1">
         <v>5</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="58"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="59"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -3347,10 +3353,10 @@
       <c r="A13" s="1">
         <v>6</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="58"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="59"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -3359,36 +3365,35 @@
       <c r="A14" s="1">
         <v>7</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="58"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="59"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="71" t="s">
+      <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="56" t="s">
+      <c r="B15" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="58"/>
-      <c r="E15" s="6" t="s">
+      <c r="C15" s="67"/>
+      <c r="D15" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="66">
+      <c r="E15" s="68"/>
+      <c r="F15" s="69">
         <v>46225</v>
       </c>
-      <c r="G15" s="67"/>
-      <c r="H15" s="68"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="25">
     <mergeCell ref="F15:H15"/>
-    <mergeCell ref="A15:B15"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="B11:C11"/>
@@ -3399,7 +3404,8 @@
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="D14:E14"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -3430,179 +3436,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="21" t="s">
-        <v>85</v>
+      <c r="E1" s="20" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="9"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="12" t="s">
+      <c r="B3" s="51"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="52" t="s">
+      <c r="B5" s="52"/>
+      <c r="C5" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
     </row>
     <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="52" t="s">
+      <c r="B6" s="52"/>
+      <c r="C6" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
     </row>
     <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="52" t="s">
+      <c r="B7" s="52"/>
+      <c r="C7" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
     </row>
     <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="53"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
+      <c r="A8" s="54"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
     </row>
     <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
     </row>
     <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="75"/>
-      <c r="C10" s="20" t="s">
+      <c r="B10" s="76"/>
+      <c r="C10" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="14"/>
+      <c r="E10" s="13"/>
     </row>
     <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="24" t="s">
+      <c r="B11" s="74"/>
+      <c r="C11" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="14"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="13"/>
     </row>
     <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="24" t="s">
+      <c r="B12" s="46"/>
+      <c r="C12" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="14"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="13"/>
     </row>
     <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="24" t="s">
+      <c r="B13" s="74"/>
+      <c r="C13" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="14"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="13"/>
     </row>
     <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="73" t="s">
+      <c r="A14" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="73"/>
-      <c r="C14" s="24" t="s">
+      <c r="B14" s="74"/>
+      <c r="C14" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="14"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="13"/>
     </row>
     <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="73" t="s">
+      <c r="A15" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="73"/>
-      <c r="C15" s="24" t="s">
+      <c r="B15" s="74"/>
+      <c r="C15" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="14"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="73" t="s">
+      <c r="A16" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="73"/>
-      <c r="C16" s="24" t="s">
+      <c r="B16" s="74"/>
+      <c r="C16" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="E16" s="14"/>
+      <c r="D16" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="13"/>
     </row>
     <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="55"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="14"/>
+      <c r="A17" s="56"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3644,367 +3650,367 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="78"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="28"/>
+      <c r="E2" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="81"/>
+      <c r="H2" s="82"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="80" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="81"/>
+      <c r="H3" s="82"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="82"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="77" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="77" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="77"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="80" t="s">
+        <v>148</v>
+      </c>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="84"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="85"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="27">
+        <v>1</v>
+      </c>
+      <c r="B9" s="77" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="27">
+        <v>2</v>
+      </c>
+      <c r="B10" s="77" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="27">
+        <v>1</v>
+      </c>
+      <c r="B12" s="77" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="79" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="81"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="79" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="80"/>
-      <c r="H3" s="81"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="81"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="76" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="76" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="79" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" s="82"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="83"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="84" t="s">
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="27">
+        <v>2</v>
+      </c>
+      <c r="B13" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="27">
+        <v>3</v>
+      </c>
+      <c r="B14" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="77"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="27">
         <v>4</v>
       </c>
-      <c r="B8" s="84"/>
-      <c r="C8" s="84"/>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="28">
-        <v>1</v>
-      </c>
-      <c r="B9" s="76" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="76"/>
-      <c r="D9" s="76"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="76"/>
-      <c r="H9" s="76"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="28">
-        <v>2</v>
-      </c>
-      <c r="B10" s="76" t="s">
-        <v>146</v>
-      </c>
-      <c r="C10" s="76"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="76"/>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="84" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="84"/>
-      <c r="C11" s="84"/>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="84"/>
-      <c r="H11" s="84"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="28">
-        <v>1</v>
-      </c>
-      <c r="B12" s="76" t="s">
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="27">
+        <v>5</v>
+      </c>
+      <c r="B16" s="77"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="85" t="s">
         <v>131</v>
       </c>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="28">
-        <v>2</v>
-      </c>
-      <c r="B13" s="76" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="76"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="76"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="76"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="28">
-        <v>3</v>
-      </c>
-      <c r="B14" s="76" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="28">
-        <v>4</v>
-      </c>
-      <c r="B15" s="76"/>
-      <c r="C15" s="76"/>
-      <c r="D15" s="76"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="76"/>
-      <c r="G15" s="76"/>
-      <c r="H15" s="76"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="28">
-        <v>5</v>
-      </c>
-      <c r="B16" s="76"/>
-      <c r="C16" s="76"/>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="76"/>
-      <c r="H16" s="76"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="84" t="s">
+      <c r="B17" s="85"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="85"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B17" s="84"/>
-      <c r="C17" s="84"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="84"/>
-      <c r="G17" s="84"/>
-      <c r="H17" s="84"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="76" t="s">
+      <c r="B18" s="77"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="77"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="77"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="77"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="85" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="76"/>
-      <c r="H18" s="76"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="76"/>
-      <c r="B19" s="76"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="76"/>
-      <c r="B20" s="76"/>
-      <c r="C20" s="76"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="76"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="84" t="s">
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="85"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="84"/>
-      <c r="C21" s="84"/>
-      <c r="D21" s="84"/>
-      <c r="E21" s="84"/>
-      <c r="F21" s="84"/>
-      <c r="G21" s="84"/>
-      <c r="H21" s="84"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="76" t="s">
-        <v>135</v>
-      </c>
-      <c r="B22" s="76"/>
-      <c r="C22" s="76"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="76"/>
-      <c r="B23" s="76"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
+      <c r="A23" s="77"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="76"/>
-      <c r="B24" s="76"/>
-      <c r="C24" s="76"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
+      <c r="A24" s="77"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
     </row>
     <row r="25" spans="1:8" ht="360.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B25" s="76"/>
-      <c r="C25" s="76"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="30"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="26">
